--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCION 100/LTAIPT_A63F100.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCION 100/LTAIPT_A63F100.xlsx
@@ -109,28 +109,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>F71B19C1D9B366C65569895FF1E8A0E7</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>E5BB9C0B915B77AA17C527F3EA37A60B</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Area_de_Transparencia/Tabla%20de%20Aplicabilidad/Tabla%20de%20Aplicabilidad.pdf</t>
   </si>
   <si>
-    <t>UNIDAD DE TRANSPARENCIA Y ARCHIVO</t>
-  </si>
-  <si>
-    <t>11/01/2023</t>
-  </si>
-  <si>
     <t/>
+  </si>
+  <si>
+    <t>Transparencia y archivo</t>
+  </si>
+  <si>
+    <t>17/04/2023</t>
   </si>
 </sst>
 </file>
@@ -526,7 +526,7 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -692,19 +692,19 @@
         <v>35</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
